--- a/skills_daten.xlsx
+++ b/skills_daten.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Kategorien" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Skills'!$A$1:$N$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Skills'!$A$1:$N$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stufen'!$A$1:$H$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Kategorien'!$A$1:$C$10</definedName>
   </definedNames>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,10 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI Emoji"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -77,7 +81,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -96,6 +100,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -463,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N112"/>
+  <dimension ref="A1:N117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -587,17 +597,17 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>https://www.denner.ch/de/search?q=chili</t>
+          <t>https://skills-king.ch/c/skills-zum-essen/chili-scharf-sussigkeit/</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>https://www.migros.ch/de/search?query=peperoncini</t>
+          <t>https://www.migros.ch/de/search?query=chilis</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>https://www.coop.ch/de/search/?text=peperoncini</t>
+          <t>https://www.coop.ch/de/lebensmittel/fruechte-gemuese/frische-kraeuter-frische-gewuerze/chili-zitronengras-ingwer/c/m_0049</t>
         </is>
       </c>
     </row>
@@ -637,12 +647,31 @@
           <t>https://www.skills-box.ch/search?q=Chili</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Chili-Bonbons</t>
+        </is>
+      </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/search?q=Toxic+Waste</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="n"/>
+          <t>https://skills-king.ch/c/skills-zum-essen/chili-scharf-sussigkeit/</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Chili &amp; Scharfes</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.skills-box.ch/products/fishermans-s-friend</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Fisherman's Friend</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -677,19 +706,15 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>https://www.denner.ch/de/search?q=senf</t>
+          <t>https://www.migros.ch/de/search?query=senf%20scharf</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>https://www.migros.ch/de/search?query=senf%2Bscharf</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.coop.ch/de/search/?text=senf</t>
-        </is>
-      </c>
+          <t>https://www.coop.ch/de/search/?text=senf%20scharf</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -724,15 +749,34 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
+          <t>https://skills-king.ch/p/tabasco-mini/</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Tabasco Mini</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/scovillas-dragonfire-extreme-hot-sauce/</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Dragonfire Extreme Hot</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
           <t>https://www.migros.ch/de/search?query=tabasco</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>https://www.coop.ch/de/search/?text=tabasco</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="n"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -767,19 +811,15 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>https://www.aldi-suisse.ch/de/ergebnisse?q=wasabi</t>
+          <t>https://www.migros.ch/de/search?query=wasabi</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>https://www.migros.ch/de/search?query=wasabi</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>https://www.coop.ch/de/search/?text=wasabi</t>
-        </is>
-      </c>
+          <t>https://www.coop.ch/de/search/?text=wasabipaste</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -814,19 +854,15 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>https://www.lidl.ch/q/de-CH/search?q=zitronen</t>
+          <t>https://www.migros.ch/de/search?query=zitronen</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>https://www.migros.ch/de/search?query=zitronen</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>https://www.coop.ch/de/search/?text=zitronen</t>
-        </is>
-      </c>
+          <t>https://www.coop.ch/de/lebensmittel/fruechte-gemuese/fruechte/zitrusfruechte/zitronen-limetten/c/m_5471</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -864,14 +900,29 @@
           <t>https://www.skills-box.ch/search?q=Riechstift</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Riechstifte</t>
+        </is>
+      </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://www.skills-box.ch/products/ammola-riechstaebchen</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AmmoLa Riechstäbchen</t>
+        </is>
+      </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
           <t>https://www.skills-box.ch/products/riechstigte</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Riechstifte Einweg</t>
         </is>
       </c>
     </row>
@@ -911,16 +962,22 @@
           <t>https://www.skills-box.ch/search?q=Tiger+Balm</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Tiger Balm</t>
+        </is>
+      </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.skills-box.ch/products/ammola-riechstaebchen</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>https://www.coop.ch/de/search/?text=tiger%2Bbalm</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AmmoLa Riechstäbchen</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -955,19 +1012,15 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>https://www.aldi-suisse.ch/de/ergebnisse?q=glace</t>
+          <t>https://www.migros.ch/de/search?query=rahmglace</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>https://www.migros.ch/de/search?query=glace</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>https://www.coop.ch/de/search/?text=glace</t>
-        </is>
-      </c>
+          <t>https://www.coop.ch/de/lebensmittel/tiefgekuehlte-produkte/glace-dessert/glace-in-portionen/c/m_0671</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1002,15 +1055,19 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
+          <t>https://skills-king.ch/p/erdbeer-pfeffer-bonbons/</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
           <t>https://www.migros.ch/de/search?query=gew%C3%BCrznelken</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>https://www.coop.ch/de/search/?text=pfefferk%C3%B6rner</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="n"/>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.coop.ch/de/lebensmittel/vorraete/bouillons-gewuerze/salz-pfeffer/pfeffer/c/m_0531</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1048,8 +1105,31 @@
           <t>https://www.skills-box.ch/search?q=Brause</t>
         </is>
       </c>
-      <c r="K12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Brausepulver</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/pop-rocks/</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Pop Rocks</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/center-shock-mix/</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Center Shock</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1084,15 +1164,34 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
+          <t>https://skills-king.ch/c/aromatherapie/</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Aromatherapie</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/c/aromatherapie/roll-ons/</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Duft-Roll-Ons</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
           <t>https://www.skills-box.ch/search?q=Riechstift</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>https://www.migros.ch/de/search?query=%C3%A4therisches+%C3%B6l</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="n"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Riechstifte</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1127,17 +1226,32 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/search?q=Massage</t>
+          <t>https://www.skills-box.ch/products/magnetische-akupressurkugeln</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Magnet-Akupressurkugeln</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/products/igelball</t>
+          <t>https://skills-king.ch/p/akupressurkugeln/</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Akupressurkugeln</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/products/magnetische-akupressurkugeln</t>
+          <t>https://skills-king.ch/s/akupressur-zubehoer/</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Akupressur-Zubehör</t>
         </is>
       </c>
     </row>
@@ -1252,14 +1366,29 @@
           <t>https://www.skills-box.ch/search?q=Toxic+Waste</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Toxic Waste</t>
+        </is>
+      </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/products/death-balls-todesmutig-sauere-apfel-limette</t>
+          <t>https://skills-king.ch/c/skills-zum-essen/sauer-suessigkeit/</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Saure Süssigkeiten</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>https://www.coop.ch/de/search/?text=saure+bonbons</t>
+          <t>https://skills-king.ch/p/warheads-extreme-sour-56g/</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Warheads</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1470,12 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/search?q=Hand+Grip</t>
+          <t>https://www.skills-box.ch/products/hand-presse</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Hand Grip</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1349,9 +1483,19 @@
           <t>https://www.skills-box.ch/products/flexbar-1</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Flexbar</t>
+        </is>
+      </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/products/wrist-ball</t>
+          <t>https://skills-king.ch/c/anti-stress-ball/</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Anti-Stress-Bälle</t>
         </is>
       </c>
     </row>
@@ -1493,17 +1637,32 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/search?q=Massage</t>
+          <t>https://www.skills-box.ch/products/massage-ball</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Massageball</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/products/massage-ball</t>
+          <t>https://skills-king.ch/p/massage-erdnuss/</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Massage-Erdnuss</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s6/producttype/faszienball-faszienrolle-3965</t>
+          <t>https://skills-king.ch/s/massage-zubehoer/</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Massage-Zubehör</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1739,12 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s12/producttype/notizbuch-1673?tagIds=1230</t>
+          <t>https://www.migros.ch/de/search?query=notizbuch</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>https://www.coop.ch/de/search/?text=notizbuch</t>
+          <t>https://www.coop.ch/de/haushalt-tier/buero-papeterie/papier-bloecke-hefte/hefte/c/m_9043</t>
         </is>
       </c>
     </row>
@@ -1625,14 +1784,29 @@
           <t>https://www.skills-box.ch/search?q=Box</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Skills-Boxen</t>
+        </is>
+      </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
           <t>https://www.skills-box.ch/products/taeschli</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Täschli</t>
+        </is>
+      </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/products/sackli</t>
+          <t>https://skills-king.ch/c/notfall-skills/</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Notfall-Skills</t>
         </is>
       </c>
     </row>
@@ -1672,9 +1846,19 @@
           <t>https://www.skills-box.ch/products/schluesselanhaenger</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Schlüsselanhänger</t>
+        </is>
+      </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://www.skills-box.ch/products/keycup-schluesselanhaenger</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Keycup-Anhänger</t>
         </is>
       </c>
       <c r="M27" s="5" t="n"/>
@@ -1960,8 +2144,26 @@
           <t>skills-box</t>
         </is>
       </c>
-      <c r="I35" s="5" t="n"/>
-      <c r="K35" s="6" t="n"/>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/lebenskarten/</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Lebenskarten</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/lebenskarten-kinder/</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Lebenskarten für Kinder</t>
+        </is>
+      </c>
       <c r="M35" s="6" t="n"/>
     </row>
     <row r="36">
@@ -2137,14 +2339,10 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s2/producttype/garn-wolle-2752</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>https://www.coop.ch/de/search/?text=wolle</t>
-        </is>
-      </c>
+          <t>https://www.migros.ch/de/search?query=wolle</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n"/>
       <c r="M40" s="5" t="n"/>
     </row>
     <row r="41">
@@ -2180,17 +2378,17 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s5/producttype/malset-1708/subtype/malsettyp-malen-nach-zahlen-2909</t>
+          <t>https://www.skills-box.ch/products/malen-und-entspannen-achtsamkeit</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/products/malen-und-entspannen-achtsamkeit</t>
+          <t>https://skills-king.ch/p/iotobo-magnet-mandala/</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/products/ausmal-postkarten</t>
+          <t>https://www.migros.ch/de/search?query=malen%20nach%20zahlen</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2670,7 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s3/producttype/yogamatte-1238</t>
+          <t>https://www.migros.ch/de/search?query=yogamatte</t>
         </is>
       </c>
       <c r="K49" s="5" t="n"/>
@@ -2656,7 +2854,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s2/producttype/eisformen-3900/subtype/eisformtyp-eiswuerfelform-6926</t>
+          <t>https://www.coop.ch/de/search/?text=eisw%C3%BCrfel</t>
         </is>
       </c>
       <c r="M54" s="5" t="n"/>
@@ -2694,15 +2892,19 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
+          <t>https://skills-king.ch/p/akupressur-clip/</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
           <t>https://www.migros.ch/de/search?query=w%C3%A4scheklammern</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>https://www.coop.ch/de/search/?text=w%C3%A4scheklammern</t>
         </is>
       </c>
-      <c r="M55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2740,16 +2942,8 @@
           <t>https://www.skills-box.ch/products/gummiband</t>
         </is>
       </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>https://www.migros.ch/de/search?query=gummib%C3%A4nder</t>
-        </is>
-      </c>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>https://www.coop.ch/de/search/?text=gummib%C3%A4nder</t>
-        </is>
-      </c>
+      <c r="K56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2854,17 +3048,32 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/search?q=Massage</t>
+          <t>https://www.skills-box.ch/products/massageholz-dreipunkt</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Massageholz Dreipunkt</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/products/massageholz-dreipunkt</t>
+          <t>https://skills-king.ch/p/hand-roller-holz/</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Hand-Roller aus Holz</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s6/producttype/faszienball-faszienrolle-3965</t>
+          <t>https://skills-king.ch/p/fidget-roller/</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Fidget Roller</t>
         </is>
       </c>
     </row>
@@ -3014,14 +3223,29 @@
           <t>https://www.skills-box.ch/search?q=Fidget</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Fidgets</t>
+        </is>
+      </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
+          <t>https://skills-king.ch/c/fidget-toys/</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Fidget Toys</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
           <t>https://www.skills-box.ch/products/fidget-cube</t>
         </is>
       </c>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>https://www.skills-box.ch/products/pop-it</t>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Fidget Cube</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3290,31 @@
           <t>https://www.skills-box.ch/products/beisskette</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Beisskette</t>
+        </is>
+      </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>https://www.migros.ch/de/search?query=kaugummi</t>
-        </is>
-      </c>
-      <c r="M64" s="5" t="n"/>
+          <t>https://www.skills-box.ch/products/suessholz-stange</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Süssholz-Stange</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/ingwerstuecke/</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Ingwerstücke</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3333,9 +3576,19 @@
           <t>https://www.skills-box.ch/products/gefuehl-squishy</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Gefühl-Squishy</t>
+        </is>
+      </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
           <t>https://www.skills-box.ch/products/dein-wut-weg-buch</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Wut-weg-Buch</t>
         </is>
       </c>
       <c r="M71" s="6" t="n"/>
@@ -3408,7 +3661,7 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s3/producttype/yogamatte-1238</t>
+          <t>https://www.migros.ch/de/search?query=yogamatte</t>
         </is>
       </c>
       <c r="K73" s="5" t="n"/>
@@ -3522,12 +3775,12 @@
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s12/producttype/notizbuch-1673?tagIds=1230</t>
+          <t>https://www.migros.ch/de/search?query=notizbuch</t>
         </is>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>https://www.coop.ch/de/search/?text=notizbuch</t>
+          <t>https://www.coop.ch/de/haushalt-tier/buero-papeterie/papier-bloecke-hefte/hefte/c/m_9043</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3822,12 @@
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s12/producttype/heft-block-1673</t>
+          <t>https://www.migros.ch/de/search?query=notizbuch</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>https://www.coop.ch/de/search/?text=notizheft</t>
+          <t>https://www.coop.ch/de/haushalt-tier/buero-papeterie/papier-bloecke-hefte/hefte/c/m_9043</t>
         </is>
       </c>
     </row>
@@ -3646,12 +3899,12 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s12/producttype/heft-block-1673</t>
+          <t>https://www.migros.ch/de/search?query=notizbuch</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>https://www.coop.ch/de/search/?text=notizblock</t>
+          <t>https://www.coop.ch/de/haushalt-tier/buero-papeterie/papier-bloecke-hefte/hefte/c/m_9043</t>
         </is>
       </c>
       <c r="M79" s="5" t="n"/>
@@ -3802,14 +4055,29 @@
           <t>https://www.skills-box.ch/products/metall-puzzle</t>
         </is>
       </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Metall-Puzzle</t>
+        </is>
+      </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
           <t>https://www.skills-box.ch/products/mini-knobel-spiele</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Mini-Knobelspiele</t>
+        </is>
+      </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/products/wooden-intellegence</t>
+          <t>https://skills-king.ch/c/holz/</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Holz-Knobelspiele</t>
         </is>
       </c>
     </row>
@@ -3846,17 +4114,32 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/search?q=Cube</t>
+          <t>https://www.skills-box.ch/products/megaminx</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Megaminx</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/products/megaminx</t>
+          <t>https://www.skills-box.ch/products/crazy-cube</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Crazy Cube</t>
         </is>
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>https://www.skills-box.ch/products/labyrinth</t>
+          <t>https://skills-king.ch/p/magnetwuerfel-24/</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Magnetwürfel</t>
         </is>
       </c>
     </row>
@@ -4036,9 +4319,19 @@
           <t>https://www.skills-box.ch/products/mokuru</t>
         </is>
       </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Mokuru</t>
+        </is>
+      </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
           <t>https://www.skills-box.ch/products/wrist-ball</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Wrist Ball</t>
         </is>
       </c>
       <c r="M89" s="6" t="n"/>
@@ -4181,15 +4474,19 @@
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s5/producttype/puzzle-622</t>
+          <t>https://skills-king.ch/p/holz-puzzle-180/</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t>https://www.coop.ch/de/search/?text=puzzle</t>
-        </is>
-      </c>
-      <c r="M93" s="5" t="n"/>
+          <t>https://www.migros.ch/de/search?query=puzzle</t>
+        </is>
+      </c>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t>https://www.coop.ch/de/baby-kind/spielwaren/puzzle/c/m_9493</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4227,11 +4524,7 @@
           <t>https://www.skills-box.ch/products/sudoku</t>
         </is>
       </c>
-      <c r="K94" s="5" t="inlineStr">
-        <is>
-          <t>https://www.galaxus.ch/de/s12/producttype/heft-block-1673</t>
-        </is>
-      </c>
+      <c r="K94" s="5" t="n"/>
       <c r="M94" s="5" t="n"/>
     </row>
     <row r="95">
@@ -4452,12 +4745,12 @@
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>https://www.galaxus.ch/de/s12/producttype/heft-block-1673</t>
+          <t>https://www.migros.ch/de/search?query=notizbuch</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
-          <t>https://www.coop.ch/de/search/?text=notizheft</t>
+          <t>https://www.coop.ch/de/haushalt-tier/buero-papeterie/papier-bloecke-hefte/hefte/c/m_9043</t>
         </is>
       </c>
       <c r="M100" s="6" t="n"/>
@@ -4532,16 +4825,8 @@
           <t>Metronom-App auf 60 BPM einstellen. Die Synchronisierung der eigenen Atmung verstärkt den Effekt.</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>https://www.galaxus.ch/de/s1/product/wittner-maelzel-serie-810k-metronom-zubehoer-instrumente-12496767</t>
-        </is>
-      </c>
-      <c r="K102" s="5" t="inlineStr">
-        <is>
-          <t>https://www.galaxus.ch/de/s1/product/korg-metronom-ma-2-stimmgeraet-11249498</t>
-        </is>
-      </c>
+      <c r="I102" s="5" t="n"/>
+      <c r="K102" s="5" t="n"/>
       <c r="M102" s="6" t="n"/>
     </row>
     <row r="103">
@@ -4822,19 +5107,15 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>https://www.denner.ch/de/search?q=kr%C3%A4uter</t>
+          <t>https://www.migros.ch/de/search?query=kr%C3%A4utertopf</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>https://www.migros.ch/de/search?query=kr%C3%A4utertopf</t>
-        </is>
-      </c>
-      <c r="M110" s="5" t="inlineStr">
-        <is>
-          <t>https://www.coop.ch/de/search/?text=frische+kr%C3%A4uter</t>
-        </is>
-      </c>
+          <t>https://www.coop.ch/de/lebensmittel/fruechte-gemuese/frische-kraeuter-frische-gewuerze/frische-kraeuter/c/m_0045</t>
+        </is>
+      </c>
+      <c r="M110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4869,7 +5150,12 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>https://www.denner.ch/de/search?q=fr%C3%BCchte</t>
+          <t>https://www.coop.ch/de/lebensmittel/fruechte-gemuese/fruechte/c/m_0002</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Frische Früchte</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr">
@@ -4877,9 +5163,19 @@
           <t>https://www.migros.ch/de/search?query=fr%C3%BCchte</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Früchte</t>
+        </is>
+      </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
-          <t>https://www.coop.ch/de/search/?text=fr%C3%BCchte</t>
+          <t>https://www.coop.ch/de/search/?text=blumenstrauss</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Blumensträusse</t>
         </is>
       </c>
     </row>
@@ -4918,10 +5214,285 @@
       <c r="K112" s="6" t="n"/>
       <c r="M112" s="6" t="n"/>
     </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Anti-Craving</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>🫚</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Ingwer kauen</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>Kandierter oder frischer Ingwer brennt scharf und lange im Mund. Der Reiz ist stark, aber weniger aggressiv als Chili und lässt sich unterwegs unauffällig einsetzen.</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>Kandierte Ingwerstücke in einer kleinen Dose mitnehmen. Wer es milder mag: Ingwer-Zitrone-Bonbons.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/ingwerstuecke/</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Ingwerstücke</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/c/skills-zum-essen/ingwer-sussigkeit/</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Ingwer-Süssigkeiten</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>https://www.migros.ch/de/search?query=ingwer</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Ingwer frisch</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Anti-Craving</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>🖤</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Salmiak-Lakritz</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>Extrem salziges Lakritz überflutet den Geschmackssinn und zieht die Aufmerksamkeit sofort in den Mund. Wirkt bei vielen stärker als Saures.</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>Nur ein Stück auf einmal. Nicht für Kinder und nicht bei hohem Blutdruck — Lakritz treibt ihn zusätzlich hoch.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/ultra-salz-lakritz/</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Ultra Salz Lakritz</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/chili-lakritz-bonbon/</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Chili-Salmiak-Lakritz</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>Mittel</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Ablenkend</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>💍</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Akupressur-Ring über die Finger rollen</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>Der Federring wird über jeden Finger auf- und abgerollt und reizt die Akupressurpunkte. Unauffällig, ohne Schmerz, jederzeit in der Hosentasche.</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>Jeden Finger 10 – 20 Sekunden rollen, bis er kribbelt. Für den ganzen Arm gibt es die grosse Variante als Armband.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/akupressur-ring/</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Akupressur-Ring</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/massage-armband/</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Massage-Armband</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>https://www.skills-box.ch/products/fingermassage-yin-yang</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Finger-Massageringe</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>Tief</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Entspannend</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>🕷️</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Kopfmassage mit der Kopfspinne</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>Die feinen Drahtnoppen streichen über die Kopfhaut und lösen ein Gänsehaut-Gefühl aus, das viele als sofort entspannend erleben.</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>Langsam von oben nach unten ziehen, Augen schliessen. Funktioniert auch bei sich selbst.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/kopfspinne/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>Tief</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ablenkend</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>🧲</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Magnetkugeln und Magnetsteine formen</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Aus hunderten kleinen Magneten Formen bauen bindet Hände und Augen gleichzeitig. Das leise Klicken und der Widerstand der Magnete wirken beruhigend.</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Mit einem einfachen Würfel oder Ring beginnen. Nicht für Kleinkinder — verschluckte Magnete sind lebensgefährlich.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/c/magnete/</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Magnete</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/speks/</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Speks Magnetkugeln</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>https://skills-king.ch/p/magnetsteine-100/</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Magnetsteine</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N112"/>
+  <autoFilter ref="A1:N117"/>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Ungültige Stufe" error="Bitte Hoch, Mittel oder Tief wählen." promptTitle="Stufe" prompt="Hoch / Mittel / Tief" type="list">
+    <dataValidation sqref="A2:A117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Ungültige Stufe" error="Bitte Hoch, Mittel oder Tief wählen." promptTitle="Stufe" prompt="Hoch / Mittel / Tief" type="list">
       <formula1>"Hoch,Mittel,Tief"</formula1>
     </dataValidation>
   </dataValidations>
